--- a/outputs/Smooth/Smooth - High N_d_report.xlsx
+++ b/outputs/Smooth/Smooth - High N_d_report.xlsx
@@ -508,16 +508,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.082340933678075</v>
+        <v>1.150255331232108</v>
       </c>
       <c r="E4" t="n">
-        <v>1.076862274614258</v>
+        <v>1.07828369137179</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="5">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9148936232283125</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.181981829618189</v>
+        <v>1.174902680816049</v>
       </c>
       <c r="E5" t="n">
-        <v>1.038716536795163</v>
+        <v>1.024497377275441</v>
       </c>
       <c r="F5" t="n">
-        <v>-10.1217494294515</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="6">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.451431608476542</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.053973945135784</v>
+        <v>1.137946463546532</v>
       </c>
       <c r="E6" t="n">
-        <v>1.088191586848098</v>
+        <v>1.06681387961769</v>
       </c>
       <c r="F6" t="n">
-        <v>3.385575137892822</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7383552592095077</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.120721454311041</v>
+        <v>1.10797721497754</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9585990506736916</v>
+        <v>0.9465404109503427</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.568173225108991</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.664519733288557</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.08841887087693</v>
+        <v>1.080682528987201</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9585325976473185</v>
+        <v>0.9399624084356717</v>
       </c>
       <c r="F8" t="n">
-        <v>2.788644097401907</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9097742187862715</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9894406472814627</v>
+        <v>1.08911075535021</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9620988985992401</v>
+        <v>0.9427484913493578</v>
       </c>
       <c r="F9" t="n">
-        <v>6.653508096356835</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="10">
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5063920418950784</v>
+        <v>0.5255642990612626</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5787496835955799</v>
+        <v>0.57912172539058</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6000000000000014</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="13">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.687500011314283</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5470947616127595</v>
+        <v>0.5504136623610307</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5513757933032017</v>
+        <v>0.5511614809035575</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.590694179972614</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="14">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.774985878268469</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7004854595311879</v>
+        <v>0.696612685560054</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8238453425320842</v>
+        <v>0.8123657002690348</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.56864331892656</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="15">
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.548940406362576</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5443917979439354</v>
+        <v>0.5306715988689673</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5541365817217597</v>
+        <v>0.5263818038039439</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.467647669383962</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.294046365726318</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5373312111583981</v>
+        <v>0.5297658104894947</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5455467532466209</v>
+        <v>0.5535124922590758</v>
       </c>
       <c r="F16" t="n">
-        <v>3.779117097554434</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.030589119551959</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6291479497359282</v>
+        <v>0.6285448574659099</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6334408103509084</v>
+        <v>0.6384123790654898</v>
       </c>
       <c r="F17" t="n">
-        <v>-15.47029825617474</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="18">
@@ -892,16 +892,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.700000000000001</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>0.03749999999999987</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03519278491525975</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2999999999999989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10.24999983268834</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2622684996132805</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4177579505081273</v>
+        <v>0.3849001794597505</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.08333282314668</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="22">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8.999999219451778</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8379629890743615</v>
+        <v>0.8490740740740742</v>
       </c>
       <c r="E22" t="n">
-        <v>1.288349699144464</v>
+        <v>1.289914342533929</v>
       </c>
       <c r="F22" t="n">
-        <v>-17.33332814392416</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="23">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9.232000000000001</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2047407407407407</v>
+        <v>0.2231481481481481</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2552862455168161</v>
+        <v>0.2715347259476825</v>
       </c>
       <c r="F23" t="n">
-        <v>6.927999999999997</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -988,16 +988,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.308800000000002</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2370444444444444</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2394011229738834</v>
+        <v>0.2618911625508987</v>
       </c>
       <c r="F24" t="n">
-        <v>10.5352</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9.232000000000001</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2047407407407407</v>
+        <v>0.2231481481481481</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2552862455168161</v>
+        <v>0.2715347259476825</v>
       </c>
       <c r="F25" t="n">
-        <v>6.927999999999997</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
